--- a/Assets/_Project/Data/UITexts.xlsx
+++ b/Assets/_Project/Data/UITexts.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI텍스트" sheetId="1" r:id="R667241b91f3d4f51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="2" r:id="Reb371c3f67fe439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI텍스트" sheetId="1" r:id="R1c23977e42f0484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="2" r:id="R0e7d3c7f68264069"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,7 +40,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -57,6 +57,11 @@
         <x:fgColor rgb="FF1D4775"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -64,7 +69,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -92,6 +97,12 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -100,7 +111,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UITextCatalog" displayName="UITextCatalog" ref="A1:D59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UITextCatalog" displayName="UITextCatalog" ref="A1:D70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Key"/>
     <x:tableColumn id="2" name="화면"/>
@@ -1146,10 +1157,164 @@
         <x:v>{0}: 순위 번호</x:v>
       </x:c>
     </x:row>
+    <x:row r="60" ht="30" customHeight="1">
+      <x:c r="A60" s="3" t="str">
+        <x:v>combo.count</x:v>
+      </x:c>
+      <x:c r="B60" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C60" s="12" t="str">
+        <x:v>콤보 {0}</x:v>
+      </x:c>
+      <x:c r="D60" s="4" t="str">
+        <x:v>{0}: 연속 정확한 착지 횟수</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="30" customHeight="1">
+      <x:c r="A61" s="3" t="str">
+        <x:v>combo.ready</x:v>
+      </x:c>
+      <x:c r="B61" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C61" s="12" t="str">
+        <x:v>부스트 준비 완료</x:v>
+      </x:c>
+      <x:c r="D61" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="30" customHeight="1">
+      <x:c r="A62" s="3" t="str">
+        <x:v>combo.progress</x:v>
+      </x:c>
+      <x:c r="B62" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C62" s="12" t="str">
+        <x:v>부스트 충전 {0} / {1}</x:v>
+      </x:c>
+      <x:c r="D62" s="4" t="str">
+        <x:v>{0}: 현재 연속 횟수, {1}: 필요한 횟수</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="30" customHeight="1">
+      <x:c r="A63" s="3" t="str">
+        <x:v>combo.use_hint</x:v>
+      </x:c>
+      <x:c r="B63" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C63" s="12" t="str">
+        <x:v>점프한 뒤 공중에서 스페이스바를 한 번 더 눌러 부스트!</x:v>
+      </x:c>
+      <x:c r="D63" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="30" customHeight="1">
+      <x:c r="A64" s="3" t="str">
+        <x:v>combo.landing_hint</x:v>
+      </x:c>
+      <x:c r="B64" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C64" s="12" t="str">
+        <x:v>청록색 중앙에 3번 연속 착지하면 부스트를 얻습니다</x:v>
+      </x:c>
+      <x:c r="D64" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="30" customHeight="1">
+      <x:c r="A65" s="3" t="str">
+        <x:v>combo.perfect</x:v>
+      </x:c>
+      <x:c r="B65" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C65" s="12" t="str">
+        <x:v>정확한 착지!  {0} 콤보</x:v>
+      </x:c>
+      <x:c r="D65" s="4" t="str">
+        <x:v>{0}: 연속 정확한 착지 횟수</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="30" customHeight="1">
+      <x:c r="A66" s="3" t="str">
+        <x:v>combo.broken</x:v>
+      </x:c>
+      <x:c r="B66" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C66" s="12" t="str">
+        <x:v>다시 콤보에 도전!</x:v>
+      </x:c>
+      <x:c r="D66" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="30" customHeight="1">
+      <x:c r="A67" s="3" t="str">
+        <x:v>combo.used</x:v>
+      </x:c>
+      <x:c r="B67" s="3" t="str">
+        <x:v>콤보</x:v>
+      </x:c>
+      <x:c r="C67" s="12" t="str">
+        <x:v>바람 부스트!</x:v>
+      </x:c>
+      <x:c r="D67" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="30" customHeight="1">
+      <x:c r="A68" s="3" t="str">
+        <x:v>combo.shortcut</x:v>
+      </x:c>
+      <x:c r="B68" s="3" t="str">
+        <x:v>시험 지름길</x:v>
+      </x:c>
+      <x:c r="C68" s="12" t="str">
+        <x:v>부스트로 한 칸 건너뛰기</x:v>
+      </x:c>
+      <x:c r="D68" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="30" customHeight="1">
+      <x:c r="A69" s="3" t="str">
+        <x:v>combo.safe_route</x:v>
+      </x:c>
+      <x:c r="B69" s="3" t="str">
+        <x:v>시험 지름길</x:v>
+      </x:c>
+      <x:c r="C69" s="12" t="str">
+        <x:v>안전한 길</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="30" customHeight="1">
+      <x:c r="A70" s="3" t="str">
+        <x:v>combo.rejoin</x:v>
+      </x:c>
+      <x:c r="B70" s="3" t="str">
+        <x:v>시험 지름길</x:v>
+      </x:c>
+      <x:c r="C70" s="12" t="str">
+        <x:v>빠른 길 도착</x:v>
+      </x:c>
+      <x:c r="D70" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re76dcd8f128c49f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ca947106054456"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/Assets/_Project/Data/UITexts.xlsx
+++ b/Assets/_Project/Data/UITexts.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI텍스트" sheetId="1" r:id="R1c23977e42f0484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="2" r:id="R0e7d3c7f68264069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI텍스트" sheetId="1" r:id="Rf50f9257f9dd4459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="2" r:id="R11550d90725f4bfe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UITextCatalog" displayName="UITextCatalog" ref="A1:D70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UITextCatalog" displayName="UITextCatalog" ref="A1:D73" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Key"/>
     <x:tableColumn id="2" name="화면"/>
@@ -1311,10 +1311,52 @@
         <x:v>일반 문구</x:v>
       </x:c>
     </x:row>
+    <x:row r="71" ht="30" customHeight="1">
+      <x:c r="A71" s="3" t="str">
+        <x:v>mobile.jump_button</x:v>
+      </x:c>
+      <x:c r="B71" s="3" t="str">
+        <x:v>모바일 조작</x:v>
+      </x:c>
+      <x:c r="C71" s="5" t="str">
+        <x:v>점프</x:v>
+      </x:c>
+      <x:c r="D71" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="30" customHeight="1">
+      <x:c r="A72" s="3" t="str">
+        <x:v>mobile.jump_hint</x:v>
+      </x:c>
+      <x:c r="B72" s="3" t="str">
+        <x:v>모바일 조작</x:v>
+      </x:c>
+      <x:c r="C72" s="5" t="str">
+        <x:v>길게 눌러 충전 · 떼면 점프</x:v>
+      </x:c>
+      <x:c r="D72" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="30" customHeight="1">
+      <x:c r="A73" s="3" t="str">
+        <x:v>mobile.boost_hint</x:v>
+      </x:c>
+      <x:c r="B73" s="3" t="str">
+        <x:v>모바일 조작</x:v>
+      </x:c>
+      <x:c r="C73" s="5" t="str">
+        <x:v>공중에서 점프 버튼을 누르면 부스트!</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="str">
+        <x:v>일반 문구</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ca947106054456"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd57b3b2287b41ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
